--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96943</v>
+        <v>96959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96959</v>
+        <v>96960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96960</v>
+        <v>96961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96961</v>
+        <v>96965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96965</v>
+        <v>96967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,6 +798,434 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129491850</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Långskägg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Usnea longissima</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högeberg, Högeberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>333026</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6430631</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129491249</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Paulsgården, Paulsgården, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333055</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6430590</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129489948</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högeberg, Högeberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>333061</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6430619</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129490414</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95948</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Paulsgården, Paulsgården, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>333068</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6430558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96967</v>
+        <v>96971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129491249</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,48 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>95952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R5" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,48 +1122,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B6" t="n">
-        <v>95948</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R6" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96971</v>
+        <v>96979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129491249</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,48 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B5" t="n">
-        <v>95952</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R5" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,48 +1122,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>95960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R6" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,6 +1226,213 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129529252</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97595</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grönnäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>332990</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6430866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129529315</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grönnäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>333040</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6430641</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,32 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129491850</v>
+        <v>129489948</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1642</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333026</v>
+        <v>333061</v>
       </c>
       <c r="R3" t="n">
-        <v>6430631</v>
+        <v>6430619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,32 +908,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129491249</v>
+        <v>129490414</v>
       </c>
       <c r="B4" t="n">
-        <v>92824</v>
+        <v>95960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333055</v>
+        <v>333068</v>
       </c>
       <c r="R4" t="n">
-        <v>6430590</v>
+        <v>6430558</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,45 +1015,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489948</v>
+        <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>97595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Grönnäs, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333061</v>
+        <v>332990</v>
       </c>
       <c r="R5" t="n">
-        <v>6430619</v>
+        <v>6430866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,87 +1087,86 @@
           <t>2025-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ann-Charlotte Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ann-Charlotte Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129490414</v>
+        <v>129529315</v>
       </c>
       <c r="B6" t="n">
-        <v>95960</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Grönnäs, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333068</v>
+        <v>333040</v>
       </c>
       <c r="R6" t="n">
-        <v>6430558</v>
+        <v>6430641</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,19 +1193,9 @@
           <t>2025-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,222 +1210,15 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ann-Charlotte Svensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Ann-Charlotte Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>129529252</v>
-      </c>
-      <c r="B7" t="n">
-        <v>97595</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Grönnäs, Vg</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>332990</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6430866</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Ann-Charlotte Svensson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Ann-Charlotte Svensson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>129529315</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57885</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Poecile palustris</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Grönnäs, Vg</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>333040</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6430641</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Ann-Charlotte Svensson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Ann-Charlotte Svensson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>96982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>95963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R3" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B4" t="n">
-        <v>95960</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R4" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1220,6 +1220,239 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129585871</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högeberg, Högeberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>332932</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6430931</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129584235</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96323</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högeberg, Högeberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>332969</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6430985</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flertalet blåmossor vid äldre tallar uppe på bergsås</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B3" t="n">
-        <v>95963</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R3" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>95963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R4" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>95963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R3" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B4" t="n">
-        <v>95963</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R4" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1453,6 +1453,346 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129650107</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102974</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grönnäs bäckravinen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>333056</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6430561</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ett tjugotal träd i sluttningen ovanför bäcken</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129650055</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97400</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grönnäs pos4, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>333082</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6430622</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129650071</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79424</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grönnäs pos5, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>333071</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6430555</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>97011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>95992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R3" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B4" t="n">
-        <v>95963</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R4" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129529315</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129585871</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>102974</v>
+        <v>103003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97400</v>
+        <v>97429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79424</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>97011</v>
+        <v>97023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129489948</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129529315</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129585871</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103003</v>
+        <v>103015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97429</v>
+        <v>97441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>97023</v>
+        <v>97024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B3" t="n">
-        <v>96004</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R3" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>96005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R4" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129529315</v>
       </c>
       <c r="B6" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129585871</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103015</v>
+        <v>103016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97441</v>
+        <v>97442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79455</v>
+        <v>79456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>96005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R3" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B4" t="n">
-        <v>96005</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R4" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>97024</v>
+        <v>97029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103016</v>
+        <v>103021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97442</v>
+        <v>97447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79456</v>
+        <v>79461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B3" t="n">
-        <v>96010</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R3" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>96010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R4" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129489948</v>
+        <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>96010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högeberg, Högeberg, Vg</t>
+          <t>Paulsgården, Paulsgården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333061</v>
+        <v>333068</v>
       </c>
       <c r="R3" t="n">
-        <v>6430619</v>
+        <v>6430558</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,48 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129490414</v>
+        <v>129489948</v>
       </c>
       <c r="B4" t="n">
-        <v>96010</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paulsgården, Paulsgården, Vg</t>
+          <t>Högeberg, Högeberg, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333068</v>
+        <v>333061</v>
       </c>
       <c r="R4" t="n">
-        <v>6430558</v>
+        <v>6430619</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>97029</v>
+        <v>97033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103021</v>
+        <v>103025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97447</v>
+        <v>97451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129374108</v>
       </c>
       <c r="B2" t="n">
-        <v>97033</v>
+        <v>97035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103025</v>
+        <v>103027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97451</v>
+        <v>97453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129490414</v>
       </c>
       <c r="B3" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129529252</v>
       </c>
       <c r="B5" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103027</v>
+        <v>103037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97453</v>
+        <v>97463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -1225,7 +1225,7 @@
         <v>129585871</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103037</v>
+        <v>103041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97463</v>
+        <v>97467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79461</v>
+        <v>79464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -1225,7 +1225,7 @@
         <v>129585871</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129584235</v>
       </c>
       <c r="B8" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103041</v>
+        <v>103044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97467</v>
+        <v>97470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79464</v>
+        <v>79467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51991-2025 artfynd.xlsx
+++ b/artfynd/A 51991-2025 artfynd.xlsx
@@ -1458,7 +1458,7 @@
         <v>129650107</v>
       </c>
       <c r="B9" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129650055</v>
       </c>
       <c r="B10" t="n">
-        <v>97470</v>
+        <v>97471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>129650071</v>
       </c>
       <c r="B11" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
